--- a/base_datas/media_porte_detalhamento.xlsx
+++ b/base_datas/media_porte_detalhamento.xlsx
@@ -603,25 +603,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>549.4168163591125</v>
+        <v>548.8169056239656</v>
       </c>
       <c r="C2">
-        <v>156.3808654497147</v>
+        <v>145.60150285684</v>
       </c>
       <c r="D2">
-        <v>5819.975403108084</v>
+        <v>5817.022423790995</v>
       </c>
       <c r="E2">
-        <v>299.7682831078441</v>
+        <v>268.5617410858967</v>
       </c>
       <c r="F2">
-        <v>500.9684538778369</v>
+        <v>500.436800890688</v>
       </c>
       <c r="G2">
-        <v>45.69707978517246</v>
+        <v>45.64839651999486</v>
       </c>
       <c r="H2">
-        <v>19.36177749173573</v>
+        <v>19.31908864253632</v>
       </c>
       <c r="I2">
         <v>213.9986885548085</v>
@@ -630,22 +630,22 @@
         <v>63.35114646392111</v>
       </c>
       <c r="K2">
-        <v>41.79611196211873</v>
+        <v>1.625138083218453</v>
       </c>
       <c r="L2">
-        <v>3434.642889720832</v>
+        <v>3431.594365360173</v>
       </c>
       <c r="M2">
-        <v>1375.54954108741</v>
+        <v>1376.536401546024</v>
       </c>
       <c r="N2">
-        <v>1010.541067624392</v>
+        <v>1009.649652119121</v>
       </c>
       <c r="O2">
-        <v>191.8394710254275</v>
+        <v>167.7215676508033</v>
       </c>
       <c r="P2">
-        <v>87.56514912812386</v>
+        <v>74.58735339158999</v>
       </c>
       <c r="Q2">
         <v>2.008150827839334</v>
@@ -654,28 +654,28 @@
         <v>20.17443846114332</v>
       </c>
       <c r="S2">
-        <v>61.82858246127102</v>
+        <v>61.59190546198231</v>
       </c>
       <c r="T2">
-        <v>69.62599818534926</v>
+        <v>69.53069226061919</v>
       </c>
       <c r="U2">
-        <v>59.31618941320696</v>
+        <v>59.28552607719175</v>
       </c>
       <c r="V2">
-        <v>211.7413586901639</v>
+        <v>211.6410376173709</v>
       </c>
       <c r="W2">
-        <v>161.5135713575636</v>
+        <v>161.2044907743951</v>
       </c>
       <c r="Z2">
-        <v>6.37950982920562</v>
+        <v>6.385982560762007</v>
       </c>
       <c r="AA2">
-        <v>22.54571592252723</v>
+        <v>22.52611134129723</v>
       </c>
       <c r="AB2">
-        <v>29.88003592395086</v>
+        <v>29.84944123414933</v>
       </c>
       <c r="AC2">
         <v>1.462972737227358E-16</v>
@@ -690,28 +690,28 @@
         <v>37.57785826801359</v>
       </c>
       <c r="AG2">
-        <v>9.655502130850087</v>
+        <v>9.386240744545658</v>
       </c>
       <c r="AH2">
-        <v>2025.10396307044</v>
+        <v>2026.596572199104</v>
       </c>
       <c r="AJ2">
-        <v>166.6917629813262</v>
+        <v>166.2920715324896</v>
       </c>
       <c r="AK2">
-        <v>585.4099754447005</v>
+        <v>585.7563267847196</v>
       </c>
       <c r="AL2">
-        <v>125.2154306289127</v>
+        <v>125.3038367144453</v>
       </c>
       <c r="AM2">
         <v>507.0945920514752</v>
       </c>
       <c r="AN2">
-        <v>32.26031691751002</v>
+        <v>32.24504983922245</v>
       </c>
       <c r="AO2">
-        <v>135.7149862436033</v>
+        <v>130.8828014690305</v>
       </c>
       <c r="AP2">
         <v>1054.011340318775</v>
@@ -726,10 +726,10 @@
         <v>11.28991989908589</v>
       </c>
       <c r="AT2">
-        <v>33.37480272920787</v>
+        <v>33.38214576431715</v>
       </c>
       <c r="AU2">
-        <v>123.0610086994272</v>
+        <v>123.1304796480703</v>
       </c>
       <c r="AV2">
         <v>1</v>
@@ -881,49 +881,49 @@
         </is>
       </c>
       <c r="B4">
-        <v>683.7584210499662</v>
+        <v>685.8385186321739</v>
       </c>
       <c r="C4">
-        <v>165.7814756011512</v>
+        <v>166.0286802373289</v>
       </c>
       <c r="D4">
-        <v>5065.801296550819</v>
+        <v>5080.695589025634</v>
       </c>
       <c r="E4">
-        <v>320.2900648269564</v>
+        <v>321.0135499668232</v>
       </c>
       <c r="F4">
-        <v>620.7603198999205</v>
+        <v>622.6274892959447</v>
       </c>
       <c r="G4">
-        <v>60.82683470883153</v>
+        <v>61.03406799670477</v>
       </c>
       <c r="H4">
         <v>13.12172856653987</v>
       </c>
       <c r="I4">
-        <v>198.0056360777324</v>
+        <v>198.3831205171551</v>
       </c>
       <c r="J4">
-        <v>71.12428371284993</v>
+        <v>71.23288213107989</v>
       </c>
       <c r="K4">
-        <v>1.435064217402416</v>
+        <v>1.439663782201782</v>
       </c>
       <c r="L4">
-        <v>2855.738711263837</v>
+        <v>2863.78284965883</v>
       </c>
       <c r="M4">
-        <v>1256.971256477495</v>
+        <v>1260.717188810657</v>
       </c>
       <c r="N4">
-        <v>953.0913288094873</v>
+        <v>956.1955505561463</v>
       </c>
       <c r="O4">
-        <v>186.0340127521739</v>
+        <v>186.2958877736952</v>
       </c>
       <c r="P4">
-        <v>102.2626672666544</v>
+        <v>102.4224924712833</v>
       </c>
       <c r="Q4">
         <v>2.427611934003728</v>
@@ -932,31 +932,31 @@
         <v>8.3146730514505</v>
       </c>
       <c r="S4">
-        <v>72.877249041577</v>
+        <v>73.10718804598574</v>
       </c>
       <c r="T4">
-        <v>126.6123586163441</v>
+        <v>127.0509752597077</v>
       </c>
       <c r="U4">
-        <v>64.3359090609473</v>
+        <v>64.46592582217509</v>
       </c>
       <c r="V4">
-        <v>254.3345124839394</v>
+        <v>255.1145115337306</v>
       </c>
       <c r="W4">
-        <v>175.8423026596535</v>
+        <v>176.3135500486563</v>
       </c>
       <c r="Z4">
-        <v>5.401038509925935</v>
+        <v>5.42194575577081</v>
       </c>
       <c r="AA4">
-        <v>30.22706301899838</v>
+        <v>30.30983500790254</v>
       </c>
       <c r="AB4">
-        <v>37.03694031171195</v>
+        <v>37.18069653664745</v>
       </c>
       <c r="AC4">
-        <v>5.658314569561789E-17</v>
+        <v>5.670922463077174E-17</v>
       </c>
       <c r="AD4">
         <v>3.190395392481452</v>
@@ -971,43 +971,43 @@
         <v>4.061797982094433</v>
       </c>
       <c r="AH4">
-        <v>1469.51707718747</v>
+        <v>1473.598753156024</v>
       </c>
       <c r="AJ4">
-        <v>190.1909038082175</v>
+        <v>190.6971872657343</v>
       </c>
       <c r="AK4">
-        <v>559.214492123717</v>
+        <v>560.6263846952579</v>
       </c>
       <c r="AL4">
-        <v>119.9838514378827</v>
+        <v>120.2987940549248</v>
       </c>
       <c r="AM4">
-        <v>496.8539187699448</v>
+        <v>497.8994169413661</v>
       </c>
       <c r="AN4">
-        <v>27.31823979749747</v>
+        <v>27.38061696784326</v>
       </c>
       <c r="AO4">
-        <v>113.4366461517572</v>
+        <v>113.8030001064159</v>
       </c>
       <c r="AP4">
-        <v>941.95379219414</v>
+        <v>944.0560276845661</v>
       </c>
       <c r="AQ4">
-        <v>135.7304527780872</v>
+        <v>136.0737077512509</v>
       </c>
       <c r="AR4">
-        <v>90.43741694040284</v>
+        <v>90.56410489177109</v>
       </c>
       <c r="AS4">
-        <v>8.230883145684309</v>
+        <v>8.247913194688397</v>
       </c>
       <c r="AT4">
-        <v>36.28730856384785</v>
+        <v>36.04461358453224</v>
       </c>
       <c r="AU4">
-        <v>94.7579890947204</v>
+        <v>94.94195540389462</v>
       </c>
       <c r="AV4">
         <v>1</v>
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>537.4842461897815</v>
+        <v>538.2360302218406</v>
       </c>
       <c r="C6">
-        <v>145.8350233121616</v>
+        <v>145.9750996736913</v>
       </c>
       <c r="D6">
-        <v>6777.820980552787</v>
+        <v>6782.806063695369</v>
       </c>
       <c r="E6">
-        <v>341.9319310618565</v>
+        <v>342.3218287143162</v>
       </c>
       <c r="F6">
-        <v>493.7402550855253</v>
+        <v>494.0191847610069</v>
       </c>
       <c r="G6">
-        <v>42.97869166236818</v>
+        <v>43.02525198275523</v>
       </c>
       <c r="H6">
         <v>16.44112935365808</v>
@@ -1183,25 +1183,25 @@
         <v>251.1050212750399</v>
       </c>
       <c r="J6">
-        <v>60.69180419765182</v>
+        <v>60.75271221100069</v>
       </c>
       <c r="K6">
         <v>4.920998016608243</v>
       </c>
       <c r="L6">
-        <v>3895.671970125964</v>
+        <v>3898.518406116009</v>
       </c>
       <c r="M6">
-        <v>1865.314142148929</v>
+        <v>1866.647942940687</v>
       </c>
       <c r="N6">
-        <v>1020.207691702378</v>
+        <v>1021.018006735832</v>
       </c>
       <c r="O6">
-        <v>214.8899935457529</v>
+        <v>215.2538965359213</v>
       </c>
       <c r="P6">
-        <v>100.0858426013677</v>
+        <v>100.0545428986505</v>
       </c>
       <c r="Q6">
         <v>12.644889366042</v>
@@ -1210,28 +1210,28 @@
         <v>10.3748421753258</v>
       </c>
       <c r="S6">
-        <v>71.62453265078564</v>
+        <v>71.74542089260071</v>
       </c>
       <c r="T6">
-        <v>39.26290613606073</v>
+        <v>39.29688814244363</v>
       </c>
       <c r="U6">
-        <v>81.74264909013803</v>
+        <v>81.71342389125941</v>
       </c>
       <c r="V6">
-        <v>210.111799864798</v>
+        <v>210.2774181265772</v>
       </c>
       <c r="W6">
-        <v>161.9513043463944</v>
+        <v>162.0594695976051</v>
       </c>
       <c r="Z6">
-        <v>5.873110445206992</v>
+        <v>5.880019986907235</v>
       </c>
       <c r="AA6">
-        <v>18.72954605488631</v>
+        <v>18.74783422235306</v>
       </c>
       <c r="AB6">
-        <v>29.97873730972622</v>
+        <v>30.00576260598434</v>
       </c>
       <c r="AC6">
         <v>5.230470492887485E-16</v>
@@ -1249,43 +1249,43 @@
         <v>4.367556505223785</v>
       </c>
       <c r="AH6">
-        <v>2566.838227197294</v>
+        <v>2568.632701263849</v>
       </c>
       <c r="AJ6">
         <v>180.5926039493764</v>
       </c>
       <c r="AK6">
-        <v>582.8359420469742</v>
+        <v>583.3069352314076</v>
       </c>
       <c r="AL6">
-        <v>123.4677028034574</v>
+        <v>123.5702054424102</v>
       </c>
       <c r="AM6">
-        <v>412.3096269234639</v>
+        <v>412.9181942673353</v>
       </c>
       <c r="AN6">
-        <v>46.24339732547907</v>
+        <v>46.27913069868823</v>
       </c>
       <c r="AO6">
-        <v>167.9305036629727</v>
+        <v>168.0309234651965</v>
       </c>
       <c r="AP6">
-        <v>1459.627252379614</v>
+        <v>1460.71188652951</v>
       </c>
       <c r="AQ6">
-        <v>140.5050215061677</v>
+        <v>140.6215044250974</v>
       </c>
       <c r="AR6">
-        <v>107.2173507749408</v>
+        <v>107.3130498498863</v>
       </c>
       <c r="AS6">
         <v>13.88469349236327</v>
       </c>
       <c r="AT6">
-        <v>27.83126489252297</v>
+        <v>27.9066997503369</v>
       </c>
       <c r="AU6">
-        <v>168.6361543834746</v>
+        <v>168.7116749021605</v>
       </c>
       <c r="AV6">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         <v>2977.957772341208</v>
       </c>
       <c r="E8">
-        <v>498.7227031586557</v>
+        <v>498.7227031586556</v>
       </c>
       <c r="F8">
         <v>1883.160899698387</v>
@@ -1594,7 +1594,7 @@
         <v>10886.22149975636</v>
       </c>
       <c r="E9">
-        <v>544.6019384373367</v>
+        <v>545.0341621980012</v>
       </c>
       <c r="F9">
         <v>524.5863053096084</v>
